--- a/assets/constructions/examples/ctd_eths_squareholder.xlsx
+++ b/assets/constructions/examples/ctd_eths_squareholder.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:AA6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,11 +544,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VDI-B1-30x20x40</t>
+          <t>VDI-B4-30x20x40</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -581,7 +601,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>INVERTED</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +621,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -611,7 +631,7 @@
         <v>90</v>
       </c>
       <c r="O2" t="n">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="P2" t="n">
         <v>40</v>
@@ -639,11 +659,17 @@
           <t>2020 / KFH Website</t>
         </is>
       </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VDI-D2-40x25x72</t>
+          <t>VDI-B1-40x25x44</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -651,16 +677,8 @@
           <t>KFH</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>VDI HOLDERS</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>DIN 69880</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>DIN_69880_1:VDI40</t>
@@ -671,12 +689,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>NEUTRAL</t>
+          <t>RADIAL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>INVERTED</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -686,29 +704,33 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>ISO_5610:25X25</t>
+          <t>KFH_VDI-25</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ISO</t>
+          <t>KFH</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>90</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
       <c r="O3" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="P3" t="n">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="Q3" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="R3" t="n">
         <v>25</v>
@@ -719,34 +741,34 @@
       <c r="T3" t="b">
         <v>0</v>
       </c>
-      <c r="U3" t="b">
-        <v>0</v>
-      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2020 / KFH Website</t>
-        </is>
-      </c>
+          <t>2016/KFH_Вспомогательный инструмент_2016_NEW!!!_ENG.pdf</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>309.90.12</t>
+          <t>VDIB3M302040</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KEMMLER</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>309</t>
-        </is>
-      </c>
+          <t>WIDIA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
@@ -763,7 +785,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>INVERTED</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -773,17 +795,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>KEM_D2-20</t>
+          <t>WID_VDI-20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Kemmler</t>
+          <t>WIDIA</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>R</t>
         </is>
       </c>
       <c r="M4" t="n">
@@ -793,13 +815,13 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="P4" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="Q4" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="R4" t="n">
         <v>20</v>
@@ -816,26 +838,40 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Kemmler_2017_Katalog_Catalogue_Online.pdf</t>
-        </is>
-      </c>
+          <t>2017/widia-2017-FullCatalogue.pdf</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VDIB3M302040</t>
+          <t>VDI-D2-40x25x72</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>WIDIA</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>KFH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>VDI HOLDERS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DIN 69880</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DIN_69880_1:VDI30</t>
+          <t>DIN_69880_1:VDI40</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -843,7 +879,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>RADIAL</t>
+          <t>NEUTRAL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -853,79 +889,79 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ISO_5610:20X20</t>
+          <t>ISO_5610:25X25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>WID_VDI-20</t>
+          <t>ISO_5610:25X25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>WIDIA</t>
+          <t>ISO</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
+          <t>N</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>91</v>
+      </c>
+      <c r="P5" t="n">
         <v>90</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>73</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
+        <v>72</v>
+      </c>
+      <c r="R5" t="n">
+        <v>25</v>
+      </c>
+      <c r="S5" t="n">
         <v>40</v>
       </c>
-      <c r="Q5" t="n">
-        <v>70</v>
-      </c>
-      <c r="R5" t="n">
-        <v>20</v>
-      </c>
-      <c r="S5" t="n">
-        <v>30</v>
-      </c>
       <c r="T5" t="b">
         <v>0</v>
       </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="U5" t="b">
+        <v>0</v>
+      </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2017/widia-2017-FullCatalogue.pdf</t>
-        </is>
-      </c>
+          <t>2020 / KFH Website</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>VDI-B4-30x20x40</t>
+          <t>309.90.12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KFH</t>
+          <t>KEMMLER</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VDI HOLDERS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>DIN 69880</t>
-        </is>
-      </c>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>DIN_69880_1:VDI30</t>
@@ -941,7 +977,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>INVERTED</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -951,33 +987,33 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>ISO_5610:20X20</t>
+          <t>KEM_D2-20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>ISO</t>
+          <t>Kemmler</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>N</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="N6" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="P6" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Q6" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="R6" t="n">
         <v>20</v>
@@ -988,17 +1024,21 @@
       <c r="T6" t="b">
         <v>0</v>
       </c>
-      <c r="U6" t="b">
-        <v>0</v>
-      </c>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>2020 / KFH Website</t>
-        </is>
-      </c>
+          <t>Kemmler_2017_Katalog_Catalogue_Online.pdf</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
